--- a/final_data_pipeline/output/311314_elec_options.xlsx
+++ b/final_data_pipeline/output/311314_elec_options.xlsx
@@ -819,7 +819,7 @@
         <v>78</v>
       </c>
       <c r="AD2">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE2">
         <v>8000</v>
@@ -908,7 +908,7 @@
         <v>78</v>
       </c>
       <c r="AD3">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE3">
         <v>8000</v>
@@ -1003,7 +1003,7 @@
         <v>78</v>
       </c>
       <c r="AD4">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE4">
         <v>8000</v>
@@ -1098,7 +1098,7 @@
         <v>78</v>
       </c>
       <c r="AD5">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE5">
         <v>8000</v>
@@ -1187,7 +1187,7 @@
         <v>78</v>
       </c>
       <c r="AD6">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE6">
         <v>8000</v>
@@ -1276,7 +1276,7 @@
         <v>78</v>
       </c>
       <c r="AD7">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE7">
         <v>8000</v>
@@ -1365,7 +1365,7 @@
         <v>78</v>
       </c>
       <c r="AD8">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE8">
         <v>8000</v>
@@ -1460,7 +1460,7 @@
         <v>78</v>
       </c>
       <c r="AD9">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE9">
         <v>8000</v>
@@ -1549,7 +1549,7 @@
         <v>78</v>
       </c>
       <c r="AD10">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE10">
         <v>8000</v>
@@ -1644,7 +1644,7 @@
         <v>78</v>
       </c>
       <c r="AD11">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE11">
         <v>8000</v>
@@ -1733,7 +1733,7 @@
         <v>78</v>
       </c>
       <c r="AD12">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE12">
         <v>8000</v>
@@ -1822,7 +1822,7 @@
         <v>78</v>
       </c>
       <c r="AD13">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE13">
         <v>8000</v>
@@ -1911,7 +1911,7 @@
         <v>78</v>
       </c>
       <c r="AD14">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE14">
         <v>8000</v>
@@ -2000,7 +2000,7 @@
         <v>78</v>
       </c>
       <c r="AD15">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE15">
         <v>8000</v>
@@ -2095,7 +2095,7 @@
         <v>78</v>
       </c>
       <c r="AD16">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE16">
         <v>8000</v>
@@ -2190,7 +2190,7 @@
         <v>78</v>
       </c>
       <c r="AD17">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE17">
         <v>8000</v>
@@ -2279,7 +2279,7 @@
         <v>78</v>
       </c>
       <c r="AD18">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE18">
         <v>8000</v>
@@ -2368,7 +2368,7 @@
         <v>78</v>
       </c>
       <c r="AD19">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE19">
         <v>8000</v>
@@ -2457,7 +2457,7 @@
         <v>78</v>
       </c>
       <c r="AD20">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE20">
         <v>8000</v>
@@ -2552,7 +2552,7 @@
         <v>78</v>
       </c>
       <c r="AD21">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE21">
         <v>8000</v>
@@ -2647,7 +2647,7 @@
         <v>78</v>
       </c>
       <c r="AD22">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE22">
         <v>8000</v>
@@ -2736,7 +2736,7 @@
         <v>78</v>
       </c>
       <c r="AD23">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE23">
         <v>8000</v>
@@ -2825,7 +2825,7 @@
         <v>78</v>
       </c>
       <c r="AD24">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE24">
         <v>8000</v>
@@ -2914,7 +2914,7 @@
         <v>78</v>
       </c>
       <c r="AD25">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE25">
         <v>8000</v>
@@ -3003,7 +3003,7 @@
         <v>78</v>
       </c>
       <c r="AD26">
-        <v>10</v>
+        <v>18.89814814814816</v>
       </c>
       <c r="AE26">
         <v>8000</v>
@@ -3092,7 +3092,7 @@
         <v>78</v>
       </c>
       <c r="AD27">
-        <v>10</v>
+        <v>18.89814814814816</v>
       </c>
       <c r="AE27">
         <v>8000</v>
@@ -3181,7 +3181,7 @@
         <v>78</v>
       </c>
       <c r="AD28">
-        <v>10</v>
+        <v>18.89814814814816</v>
       </c>
       <c r="AE28">
         <v>8000</v>
@@ -3270,7 +3270,7 @@
         <v>78</v>
       </c>
       <c r="AD29">
-        <v>10</v>
+        <v>18.89814814814816</v>
       </c>
       <c r="AE29">
         <v>8000</v>
@@ -3359,7 +3359,7 @@
         <v>78</v>
       </c>
       <c r="AD30">
-        <v>10</v>
+        <v>18.89814814814816</v>
       </c>
       <c r="AE30">
         <v>8000</v>
@@ -3448,7 +3448,7 @@
         <v>78</v>
       </c>
       <c r="AD31">
-        <v>10</v>
+        <v>18.89814814814816</v>
       </c>
       <c r="AE31">
         <v>8000</v>
@@ -3537,7 +3537,7 @@
         <v>78</v>
       </c>
       <c r="AD32">
-        <v>10</v>
+        <v>18.89814814814816</v>
       </c>
       <c r="AE32">
         <v>8000</v>
@@ -3626,7 +3626,7 @@
         <v>78</v>
       </c>
       <c r="AD33">
-        <v>10</v>
+        <v>18.89814814814816</v>
       </c>
       <c r="AE33">
         <v>8000</v>
@@ -3715,7 +3715,7 @@
         <v>78</v>
       </c>
       <c r="AD34">
-        <v>10</v>
+        <v>18.89814814814816</v>
       </c>
       <c r="AE34">
         <v>8000</v>
@@ -3804,7 +3804,7 @@
         <v>78</v>
       </c>
       <c r="AD35">
-        <v>10</v>
+        <v>18.89814814814816</v>
       </c>
       <c r="AE35">
         <v>8000</v>
@@ -3893,7 +3893,7 @@
         <v>78</v>
       </c>
       <c r="AD36">
-        <v>10</v>
+        <v>18.89814814814816</v>
       </c>
       <c r="AE36">
         <v>8000</v>
@@ -3982,7 +3982,7 @@
         <v>78</v>
       </c>
       <c r="AD37">
-        <v>10</v>
+        <v>18.89814814814816</v>
       </c>
       <c r="AE37">
         <v>8000</v>
@@ -4071,7 +4071,7 @@
         <v>78</v>
       </c>
       <c r="AD38">
-        <v>10</v>
+        <v>18.89814814814816</v>
       </c>
       <c r="AE38">
         <v>8000</v>
@@ -4160,7 +4160,7 @@
         <v>78</v>
       </c>
       <c r="AD39">
-        <v>10</v>
+        <v>18.89814814814816</v>
       </c>
       <c r="AE39">
         <v>8000</v>
@@ -4249,7 +4249,7 @@
         <v>78</v>
       </c>
       <c r="AD40">
-        <v>10</v>
+        <v>18.89814814814816</v>
       </c>
       <c r="AE40">
         <v>8000</v>
@@ -4338,7 +4338,7 @@
         <v>78</v>
       </c>
       <c r="AD41">
-        <v>10</v>
+        <v>18.89814814814816</v>
       </c>
       <c r="AE41">
         <v>8000</v>
@@ -4433,7 +4433,7 @@
         <v>78</v>
       </c>
       <c r="AD42">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE42">
         <v>8000</v>
@@ -4522,7 +4522,7 @@
         <v>78</v>
       </c>
       <c r="AD43">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE43">
         <v>8000</v>
@@ -4611,7 +4611,7 @@
         <v>78</v>
       </c>
       <c r="AD44">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE44">
         <v>8000</v>
@@ -4706,7 +4706,7 @@
         <v>78</v>
       </c>
       <c r="AD45">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE45">
         <v>8000</v>
@@ -4795,7 +4795,7 @@
         <v>78</v>
       </c>
       <c r="AD46">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE46">
         <v>8000</v>
@@ -4890,7 +4890,7 @@
         <v>78</v>
       </c>
       <c r="AD47">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE47">
         <v>8000</v>
@@ -4985,7 +4985,7 @@
         <v>78</v>
       </c>
       <c r="AD48">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE48">
         <v>8000</v>
@@ -5080,7 +5080,7 @@
         <v>78</v>
       </c>
       <c r="AD49">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE49">
         <v>8000</v>
@@ -5175,7 +5175,7 @@
         <v>78</v>
       </c>
       <c r="AD50">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE50">
         <v>8000</v>
@@ -5264,7 +5264,7 @@
         <v>78</v>
       </c>
       <c r="AD51">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE51">
         <v>8000</v>
@@ -5359,7 +5359,7 @@
         <v>78</v>
       </c>
       <c r="AD52">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE52">
         <v>8000</v>
@@ -5454,7 +5454,7 @@
         <v>78</v>
       </c>
       <c r="AD53">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE53">
         <v>8000</v>
@@ -5543,7 +5543,7 @@
         <v>78</v>
       </c>
       <c r="AD54">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE54">
         <v>8000</v>
@@ -5638,7 +5638,7 @@
         <v>78</v>
       </c>
       <c r="AD55">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE55">
         <v>8000</v>
@@ -5733,7 +5733,7 @@
         <v>78</v>
       </c>
       <c r="AD56">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE56">
         <v>8000</v>
@@ -5828,7 +5828,7 @@
         <v>78</v>
       </c>
       <c r="AD57">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE57">
         <v>8000</v>
@@ -5923,7 +5923,7 @@
         <v>78</v>
       </c>
       <c r="AD58">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE58">
         <v>8000</v>
@@ -6018,7 +6018,7 @@
         <v>78</v>
       </c>
       <c r="AD59">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE59">
         <v>8000</v>
@@ -6107,7 +6107,7 @@
         <v>78</v>
       </c>
       <c r="AD60">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE60">
         <v>8000</v>
@@ -6202,7 +6202,7 @@
         <v>78</v>
       </c>
       <c r="AD61">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE61">
         <v>8000</v>
@@ -6291,7 +6291,7 @@
         <v>78</v>
       </c>
       <c r="AD62">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE62">
         <v>8000</v>
@@ -6380,7 +6380,7 @@
         <v>78</v>
       </c>
       <c r="AD63">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE63">
         <v>8000</v>
@@ -6475,7 +6475,7 @@
         <v>78</v>
       </c>
       <c r="AD64">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE64">
         <v>8000</v>
@@ -6570,7 +6570,7 @@
         <v>78</v>
       </c>
       <c r="AD65">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE65">
         <v>8000</v>
